--- a/Bangalore-July-2025.xlsx
+++ b/Bangalore-July-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="75">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Bangalore</t>
   </si>
   <si>
@@ -181,10 +184,10 @@
     <t>KA03AK9164</t>
   </si>
   <si>
-    <t>Dzire</t>
-  </si>
-  <si>
-    <t>Crysta</t>
+    <t>DZIRE</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>HYCROSS</t>
@@ -196,10 +199,10 @@
     <t>BALENO</t>
   </si>
   <si>
-    <t>Fortuner</t>
-  </si>
-  <si>
-    <t>Celerio</t>
+    <t>FORTUNER</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>28/02/2024</t>
@@ -214,25 +217,28 @@
     <t>30/10/2021</t>
   </si>
   <si>
+    <t>15/02/2021</t>
+  </si>
+  <si>
+    <t>23/03/2021</t>
+  </si>
+  <si>
+    <t>24/03/2022</t>
+  </si>
+  <si>
+    <t>25/03/2021</t>
+  </si>
+  <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
+  </si>
+  <si>
+    <t>23/02/2023</t>
+  </si>
+  <si>
     <t>-</t>
-  </si>
-  <si>
-    <t>15/02/2021</t>
-  </si>
-  <si>
-    <t>24/03/2022</t>
-  </si>
-  <si>
-    <t>25/03/2021</t>
-  </si>
-  <si>
-    <t>23/03/2023</t>
-  </si>
-  <si>
-    <t>31/03/2023</t>
-  </si>
-  <si>
-    <t>23/02/2023</t>
   </si>
 </sst>
 </file>
@@ -594,10 +600,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z28"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,25 +682,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" s="2">
         <v>45174</v>
@@ -757,24 +766,24 @@
         <v>13.64</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2">
         <v>44205</v>
@@ -834,30 +843,30 @@
         <v>0</v>
       </c>
       <c r="Z3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H4">
         <v>51102</v>
@@ -914,30 +923,30 @@
         <v>-18785</v>
       </c>
       <c r="Z4" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5">
         <v>57634</v>
@@ -997,24 +1006,24 @@
         <v>23.47</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="2">
         <v>43560</v>
@@ -1077,27 +1086,27 @@
         <v>51.21</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>169133</v>
@@ -1157,27 +1166,27 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H8">
         <v>116064</v>
@@ -1237,27 +1246,27 @@
         <v>54.75</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9">
         <v>79037</v>
@@ -1317,27 +1326,27 @@
         <v>52.34</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10" t="s">
-        <v>66</v>
+        <v>57</v>
+      </c>
+      <c r="G10" s="2">
+        <v>44350</v>
       </c>
       <c r="H10">
         <v>80758</v>
@@ -1397,27 +1406,27 @@
         <v>58.13</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H11">
         <v>61784</v>
@@ -1474,27 +1483,27 @@
         <v>-100</v>
       </c>
       <c r="Z11" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="2">
         <v>44387</v>
@@ -1557,24 +1566,24 @@
         <v>32.47</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
         <v>67</v>
@@ -1637,24 +1646,24 @@
         <v>54.32</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2">
         <v>44257</v>
@@ -1717,24 +1726,24 @@
         <v>53.41</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2">
         <v>44387</v>
@@ -1797,27 +1806,27 @@
         <v>-36.04</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H16">
         <v>82691</v>
@@ -1882,19 +1891,19 @@
         <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" s="2">
         <v>44902</v>
@@ -1954,7 +1963,7 @@
         <v>-62373</v>
       </c>
       <c r="Z17" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:26">
@@ -1962,19 +1971,19 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" s="2">
         <v>44746</v>
@@ -2042,22 +2051,22 @@
         <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19">
         <v>62874</v>
@@ -2122,22 +2131,22 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20">
         <v>57224</v>
@@ -2202,19 +2211,19 @@
         <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
         <v>66</v>
@@ -2282,22 +2291,22 @@
         <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H22">
         <v>91798</v>
@@ -2362,22 +2371,22 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H23">
         <v>109560</v>
@@ -2442,22 +2451,22 @@
         <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H24">
         <v>108253</v>
@@ -2522,19 +2531,19 @@
         <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G25" s="2">
         <v>45174</v>
@@ -2602,19 +2611,19 @@
         <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G26" s="2">
         <v>45235</v>
@@ -2682,22 +2691,22 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H27">
         <v>39173</v>
@@ -2762,19 +2771,19 @@
         <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G28" s="2">
         <v>45174</v>
